--- a/data/trans_orig/Q17F_D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario</t>
+          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 20,08</t>
+          <t>8,47; 20,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,85</t>
+          <t>8,23; 14,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 19,63</t>
+          <t>9,44; 19,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 43,91</t>
+          <t>18,21; 44,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 11,05</t>
+          <t>6,05; 10,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,98</t>
+          <t>6,7; 12,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 17,45</t>
+          <t>9,63; 17,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,42; 34,61</t>
+          <t>18,61; 34,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,53</t>
+          <t>7,41; 12,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 12,65</t>
+          <t>8,11; 12,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 16,28</t>
+          <t>10,24; 16,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,65; 33,05</t>
+          <t>20,08; 33,99</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,69</t>
+          <t>6,55; 12,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 12,43</t>
+          <t>6,47; 12,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,05</t>
+          <t>6,5; 12,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,32; 32,65</t>
+          <t>15,41; 33,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 15,14</t>
+          <t>7,67; 14,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,69; 15,24</t>
+          <t>8,75; 14,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 23,59</t>
+          <t>11,17; 22,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,99; 24,76</t>
+          <t>14,08; 26,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 12,94</t>
+          <t>7,73; 12,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 12,78</t>
+          <t>8,24; 12,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 17,31</t>
+          <t>10,08; 16,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,47; 26,39</t>
+          <t>15,89; 25,67</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,11</t>
+          <t>4,66; 14,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 17,9</t>
+          <t>5,87; 17,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,42</t>
+          <t>4,71; 9,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 39,62</t>
+          <t>18,31; 40,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 24,36</t>
+          <t>6,47; 25,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,41</t>
+          <t>3,74; 10,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 17,54</t>
+          <t>6,32; 16,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,11; 24,23</t>
+          <t>13,28; 25,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 16,92</t>
+          <t>6,62; 18,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,09</t>
+          <t>5,57; 11,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,86</t>
+          <t>6,38; 12,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 28,27</t>
+          <t>16,57; 28,17</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 14,57</t>
+          <t>8,3; 14,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,16</t>
+          <t>8,02; 12,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 12,3</t>
+          <t>8,14; 12,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 31,1</t>
+          <t>19,05; 31,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,44</t>
+          <t>7,36; 11,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,34</t>
+          <t>8,12; 12,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 18,02</t>
+          <t>11,23; 18,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 24,64</t>
+          <t>16,28; 24,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,49</t>
+          <t>8,25; 11,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 11,52</t>
+          <t>8,61; 11,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 14,92</t>
+          <t>10,47; 14,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 25,37</t>
+          <t>18,8; 25,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q17F_D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,66</t>
+          <t>28,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,39</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>26,64</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 20,18</t>
+          <t>8,52; 19,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 14,76</t>
+          <t>8,33; 15,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 19,1</t>
+          <t>9,31; 18,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 44,23</t>
+          <t>18,39; 45,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,75</t>
+          <t>6,09; 11,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,89</t>
+          <t>6,83; 13,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 17,76</t>
+          <t>9,24; 18,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,61; 34,08</t>
+          <t>19,21; 35,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 12,58</t>
+          <t>7,55; 13,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 12,8</t>
+          <t>8,02; 12,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 16,66</t>
+          <t>10,14; 16,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,08; 33,99</t>
+          <t>21,01; 35,07</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21,39</t>
+          <t>21,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,11</t>
+          <t>22,27</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>21,71</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 12,25</t>
+          <t>6,52; 12,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 12,21</t>
+          <t>6,36; 11,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,33</t>
+          <t>6,68; 12,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 33,44</t>
+          <t>15,5; 30,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 14,57</t>
+          <t>7,52; 14,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 14,99</t>
+          <t>8,63; 14,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,17; 22,55</t>
+          <t>11,34; 23,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,08; 26,29</t>
+          <t>18,67; 27,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,87</t>
+          <t>7,96; 12,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,76</t>
+          <t>8,3; 12,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 16,81</t>
+          <t>10,05; 17,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 25,67</t>
+          <t>18,3; 26,43</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,43</t>
+          <t>28,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,46</t>
+          <t>19,43</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,55</t>
+          <t>23,56</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 14,06</t>
+          <t>4,62; 14,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 17,55</t>
+          <t>5,63; 17,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,87</t>
+          <t>4,78; 9,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,31; 40,61</t>
+          <t>19,06; 43,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 25,86</t>
+          <t>6,1; 23,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 10,51</t>
+          <t>3,74; 10,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 16,84</t>
+          <t>6,49; 18,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,28; 25,19</t>
+          <t>14,36; 27,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 18,2</t>
+          <t>6,46; 17,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 11,69</t>
+          <t>5,52; 11,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 12,1</t>
+          <t>6,51; 12,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,57; 28,17</t>
+          <t>18,0; 30,91</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,76</t>
+          <t>24,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,75</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,0</t>
+          <t>23,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 14,3</t>
+          <t>8,24; 15,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,32</t>
+          <t>8,13; 12,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 12,68</t>
+          <t>8,14; 12,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,05; 31,14</t>
+          <t>19,67; 31,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,28</t>
+          <t>7,57; 11,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 12,21</t>
+          <t>8,18; 12,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 18,18</t>
+          <t>11,21; 17,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,28; 24,32</t>
+          <t>19,39; 26,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,52</t>
+          <t>8,13; 11,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,52</t>
+          <t>8,65; 11,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 14,82</t>
+          <t>10,42; 14,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,8; 25,76</t>
+          <t>20,54; 26,65</t>
         </is>
       </c>
     </row>
